--- a/ACCY122/Tutorial/T04/T4.xlsx
+++ b/ACCY122/Tutorial/T04/T4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Tutorial/T04/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Tutorial\T04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B948C6-E4E7-8E44-9314-0534E5A63816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6B0643-DD10-4CD4-AFCE-07E66CEB65A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18740" tabRatio="802" activeTab="11" xr2:uid="{98A3E0AE-1528-4E92-82CE-4DA2D69F6A7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="802" activeTab="10" xr2:uid="{98A3E0AE-1528-4E92-82CE-4DA2D69F6A7C}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="4" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="Ex 6.8 (A)" sheetId="28" r:id="rId11"/>
     <sheet name="P 13.16 (A)" sheetId="29" r:id="rId12"/>
     <sheet name="Ex 13.5(A)" sheetId="30" r:id="rId13"/>
+    <sheet name="Ex 13.2 (A)" sheetId="32" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -94,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="205">
   <si>
     <t>Details</t>
   </si>
@@ -720,17 +721,72 @@
   <si>
     <t>?? $197,920</t>
   </si>
+  <si>
+    <t>i) FIFO</t>
+  </si>
+  <si>
+    <t>For periodic inventory system, the formula for COGS = BI + P - EI</t>
+  </si>
+  <si>
+    <t>Under periodic FIFO, ending inventory is assumed to consist of the latest purchases.</t>
+  </si>
+  <si>
+    <t>Ending Inventory Total Cost:</t>
+  </si>
+  <si>
+    <t>Cost per U</t>
+  </si>
+  <si>
+    <t>(Ending Inventory Value)</t>
+  </si>
+  <si>
+    <t>COGS = ($364500 + $1659000) - $829500 = $1194000</t>
+  </si>
+  <si>
+    <t>ii) LIFO</t>
+  </si>
+  <si>
+    <t>Under periodic LIFO, ending inventory is assumed to consist of the earliest purchases.</t>
+  </si>
+  <si>
+    <t>COGS = ($364500 + $1659000) - $744000 = $1279500</t>
+  </si>
+  <si>
+    <t>iii) WAV</t>
+  </si>
+  <si>
+    <t>Inventory + Purchase =  69 000 units</t>
+  </si>
+  <si>
+    <t>Total cost = $2023500</t>
+  </si>
+  <si>
+    <t>WAV = 2023500/69000 =  $29.33 per unit</t>
+  </si>
+  <si>
+    <t>COGS = 42000 X 29.33 = $1231860</t>
+  </si>
+  <si>
+    <t>EIV = 27000 X 29.33 = $791910</t>
+  </si>
+  <si>
+    <t>242 400</t>
+  </si>
+  <si>
+    <t>if there is Freight Outwards = Expense</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -896,6 +952,14 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -959,7 +1023,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1199,12 +1263,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1400,14 +1475,19 @@
     <xf numFmtId="166" fontId="17" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1454,8 +1534,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1098530" y="630979"/>
-          <a:ext cx="5942604" cy="5835598"/>
+          <a:off x="1017187" y="630979"/>
+          <a:ext cx="5210518" cy="5835598"/>
           <a:chOff x="0" y="78429"/>
           <a:chExt cx="6059328" cy="3928254"/>
         </a:xfrm>
@@ -1937,6 +2017,61 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>413657</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>112731</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>585829</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>22297</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05361872-8992-73B5-E8BB-7D09C7862BC0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="413657" y="112731"/>
+          <a:ext cx="5159331" cy="3148066"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2705,7 +2840,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>600227</xdr:colOff>
+      <xdr:colOff>581177</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>15516</xdr:rowOff>
     </xdr:to>
@@ -2932,7 +3067,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>799583</xdr:colOff>
+      <xdr:colOff>580424</xdr:colOff>
       <xdr:row>92</xdr:row>
       <xdr:rowOff>157808</xdr:rowOff>
     </xdr:to>
@@ -2992,8 +3127,8 @@
       <xdr:rowOff>12959</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>312532</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>396824</xdr:colOff>
       <xdr:row>95</xdr:row>
       <xdr:rowOff>171710</xdr:rowOff>
     </xdr:to>
@@ -3392,7 +3527,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B31468-06B7-4EAE-81E5-FB432EF125CF}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3402,22 +3537,22 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A939B-174C-4659-B497-77F0D3AD477A}">
   <dimension ref="A1:O83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" customWidth="1"/>
-    <col min="3" max="3" width="4.5" customWidth="1"/>
-    <col min="6" max="6" width="9.5" customWidth="1"/>
-    <col min="7" max="7" width="4.1640625" customWidth="1"/>
-    <col min="11" max="11" width="4.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="20"/>
       <c r="B2" s="20"/>
       <c r="D2" s="20"/>
@@ -3436,7 +3571,7 @@
       </c>
       <c r="N2" s="20"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>47</v>
       </c>
@@ -3471,7 +3606,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="21">
         <v>37104</v>
       </c>
@@ -3495,7 +3630,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="20"/>
       <c r="B5" s="20"/>
       <c r="D5" s="20"/>
@@ -3508,7 +3643,7 @@
       <c r="M5" s="20"/>
       <c r="N5" s="20"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>12</v>
       </c>
@@ -3544,7 +3679,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="20"/>
       <c r="B7" s="20"/>
       <c r="D7" s="20"/>
@@ -3569,7 +3704,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="20"/>
       <c r="B8" s="20"/>
       <c r="D8" s="20"/>
@@ -3582,7 +3717,7 @@
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>15</v>
       </c>
@@ -3616,7 +3751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="20"/>
       <c r="B10" s="20"/>
       <c r="D10" s="20"/>
@@ -3644,7 +3779,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="20"/>
       <c r="B11" s="20"/>
       <c r="D11" s="20"/>
@@ -3657,7 +3792,7 @@
       <c r="M11" s="20"/>
       <c r="N11" s="20"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>21</v>
       </c>
@@ -3693,7 +3828,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="20"/>
       <c r="B13" s="20"/>
       <c r="D13" s="20"/>
@@ -3718,7 +3853,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="20"/>
       <c r="B14" s="20"/>
       <c r="D14" s="20"/>
@@ -3731,7 +3866,7 @@
       <c r="M14" s="20"/>
       <c r="N14" s="20"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="20">
         <v>22</v>
       </c>
@@ -3765,7 +3900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="20"/>
       <c r="B16" s="20"/>
       <c r="D16" s="20"/>
@@ -3795,7 +3930,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="20"/>
       <c r="B17" s="20"/>
       <c r="D17" s="20"/>
@@ -3808,7 +3943,7 @@
       <c r="M17" s="20"/>
       <c r="N17" s="20"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="20">
         <v>28</v>
       </c>
@@ -3841,7 +3976,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="20"/>
       <c r="B19" s="20"/>
       <c r="D19" s="20"/>
@@ -3853,7 +3988,7 @@
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J20" s="22">
         <f>SUM(J9:J18)</f>
         <v>2915</v>
@@ -3869,12 +4004,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
       <c r="B23" s="20"/>
       <c r="D23" s="20"/>
@@ -3893,7 +4028,7 @@
       </c>
       <c r="N23" s="20"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>47</v>
       </c>
@@ -3928,7 +4063,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="21">
         <v>37104</v>
       </c>
@@ -3952,7 +4087,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="20"/>
       <c r="B26" s="20"/>
       <c r="D26" s="20"/>
@@ -3965,7 +4100,7 @@
       <c r="M26" s="20"/>
       <c r="N26" s="20"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="20">
         <v>12</v>
       </c>
@@ -4001,7 +4136,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="20"/>
       <c r="B28" s="20"/>
       <c r="D28" s="20"/>
@@ -4026,7 +4161,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="20"/>
       <c r="B29" s="20"/>
       <c r="D29" s="20"/>
@@ -4039,7 +4174,7 @@
       <c r="M29" s="20"/>
       <c r="N29" s="20"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="20">
         <v>15</v>
       </c>
@@ -4074,7 +4209,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="20"/>
       <c r="B31" s="20"/>
       <c r="D31" s="20"/>
@@ -4105,7 +4240,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="20"/>
       <c r="B32" s="20"/>
       <c r="D32" s="20"/>
@@ -4118,7 +4253,7 @@
       <c r="M32" s="24"/>
       <c r="N32" s="24"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="20">
         <v>21</v>
       </c>
@@ -4154,7 +4289,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="20"/>
       <c r="B34" s="20"/>
       <c r="D34" s="20"/>
@@ -4179,7 +4314,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="20"/>
       <c r="B35" s="20"/>
       <c r="D35" s="20"/>
@@ -4204,7 +4339,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="20"/>
       <c r="B36" s="20"/>
       <c r="D36" s="20"/>
@@ -4217,7 +4352,7 @@
       <c r="M36" s="23"/>
       <c r="N36" s="23"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="20">
         <v>22</v>
       </c>
@@ -4256,7 +4391,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="20"/>
       <c r="B38" s="20"/>
       <c r="D38" s="20"/>
@@ -4291,7 +4426,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="20"/>
       <c r="B39" s="20"/>
       <c r="D39" s="20"/>
@@ -4326,7 +4461,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="20"/>
       <c r="B40" s="20"/>
       <c r="D40" s="20"/>
@@ -4339,7 +4474,7 @@
       <c r="M40" s="23"/>
       <c r="N40" s="23"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="20">
         <v>28</v>
       </c>
@@ -4375,7 +4510,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="20"/>
       <c r="B42" s="20"/>
       <c r="D42" s="20"/>
@@ -4407,7 +4542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G43" t="s">
         <v>105</v>
       </c>
@@ -4434,7 +4569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J45" s="2">
         <f>SUM(J30:J43)</f>
         <v>2990</v>
@@ -4450,12 +4585,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="20"/>
       <c r="B47" s="20"/>
       <c r="D47" s="20"/>
@@ -4474,7 +4609,7 @@
       </c>
       <c r="N47" s="20"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="20" t="s">
         <v>47</v>
       </c>
@@ -4509,7 +4644,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="21">
         <v>37104</v>
       </c>
@@ -4533,7 +4668,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="20"/>
       <c r="B50" s="20"/>
       <c r="D50" s="20"/>
@@ -4546,7 +4681,7 @@
       <c r="M50" s="20"/>
       <c r="N50" s="20"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="20">
         <v>12</v>
       </c>
@@ -4568,7 +4703,7 @@
       <c r="M51" s="20"/>
       <c r="N51" s="20"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="20"/>
       <c r="B52" s="20"/>
       <c r="D52" s="20"/>
@@ -4581,7 +4716,7 @@
       <c r="M52" s="20"/>
       <c r="N52" s="20"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="20">
         <v>15</v>
       </c>
@@ -4598,7 +4733,7 @@
       <c r="M53" s="20"/>
       <c r="N53" s="20"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="20"/>
       <c r="B54" s="20"/>
       <c r="D54" s="20"/>
@@ -4611,7 +4746,7 @@
       <c r="M54" s="20"/>
       <c r="N54" s="20"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="20"/>
       <c r="B55" s="20"/>
       <c r="D55" s="20"/>
@@ -4624,7 +4759,7 @@
       <c r="M55" s="20"/>
       <c r="N55" s="20"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="20">
         <v>21</v>
       </c>
@@ -4646,7 +4781,7 @@
       <c r="M56" s="20"/>
       <c r="N56" s="20"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="20"/>
       <c r="B57" s="20"/>
       <c r="D57" s="20"/>
@@ -4659,7 +4794,7 @@
       <c r="M57" s="20"/>
       <c r="N57" s="20"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="20"/>
       <c r="B58" s="20"/>
       <c r="D58" s="20"/>
@@ -4672,7 +4807,7 @@
       <c r="M58" s="20"/>
       <c r="N58" s="20"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="20"/>
       <c r="B59" s="20"/>
       <c r="D59" s="20"/>
@@ -4685,7 +4820,7 @@
       <c r="M59" s="20"/>
       <c r="N59" s="20"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="20">
         <v>22</v>
       </c>
@@ -4702,7 +4837,7 @@
       <c r="M60" s="20"/>
       <c r="N60" s="20"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="20"/>
       <c r="B61" s="20"/>
       <c r="D61" s="20"/>
@@ -4715,7 +4850,7 @@
       <c r="M61" s="20"/>
       <c r="N61" s="20"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="20">
         <v>28</v>
       </c>
@@ -4732,7 +4867,7 @@
       <c r="M62" s="20"/>
       <c r="N62" s="20"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="20"/>
       <c r="B63" s="20"/>
       <c r="D63" s="20"/>
@@ -4745,12 +4880,12 @@
       <c r="M63" s="20"/>
       <c r="N63" s="20"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="20"/>
       <c r="B67" s="20"/>
       <c r="D67" s="20"/>
@@ -4769,7 +4904,7 @@
       </c>
       <c r="N67" s="20"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="20" t="s">
         <v>47</v>
       </c>
@@ -4804,7 +4939,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="21">
         <v>37104</v>
       </c>
@@ -4828,7 +4963,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="20"/>
       <c r="B70" s="20"/>
       <c r="D70" s="20"/>
@@ -4841,7 +4976,7 @@
       <c r="M70" s="20"/>
       <c r="N70" s="20"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="20">
         <v>12</v>
       </c>
@@ -4863,7 +4998,7 @@
       <c r="M71" s="20"/>
       <c r="N71" s="20"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="20"/>
       <c r="B72" s="20"/>
       <c r="D72" s="20"/>
@@ -4876,7 +5011,7 @@
       <c r="M72" s="20"/>
       <c r="N72" s="20"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="20">
         <v>15</v>
       </c>
@@ -4893,7 +5028,7 @@
       <c r="M73" s="20"/>
       <c r="N73" s="20"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="20"/>
       <c r="B74" s="20"/>
       <c r="D74" s="20"/>
@@ -4906,7 +5041,7 @@
       <c r="M74" s="20"/>
       <c r="N74" s="20"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="20"/>
       <c r="B75" s="20"/>
       <c r="D75" s="20"/>
@@ -4919,7 +5054,7 @@
       <c r="M75" s="20"/>
       <c r="N75" s="20"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="20">
         <v>21</v>
       </c>
@@ -4941,7 +5076,7 @@
       <c r="M76" s="20"/>
       <c r="N76" s="20"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="20"/>
       <c r="B77" s="20"/>
       <c r="D77" s="20"/>
@@ -4954,7 +5089,7 @@
       <c r="M77" s="20"/>
       <c r="N77" s="20"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="20"/>
       <c r="B78" s="20"/>
       <c r="D78" s="20"/>
@@ -4967,7 +5102,7 @@
       <c r="M78" s="20"/>
       <c r="N78" s="20"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="20"/>
       <c r="B79" s="20"/>
       <c r="D79" s="20"/>
@@ -4980,7 +5115,7 @@
       <c r="M79" s="20"/>
       <c r="N79" s="20"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="20">
         <v>22</v>
       </c>
@@ -4997,7 +5132,7 @@
       <c r="M80" s="20"/>
       <c r="N80" s="20"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="20"/>
       <c r="B81" s="20"/>
       <c r="D81" s="20"/>
@@ -5010,7 +5145,7 @@
       <c r="M81" s="20"/>
       <c r="N81" s="20"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="20">
         <v>28</v>
       </c>
@@ -5027,7 +5162,7 @@
       <c r="M82" s="20"/>
       <c r="N82" s="20"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="20"/>
       <c r="B83" s="20"/>
       <c r="D83" s="20"/>
@@ -5049,24 +5184,24 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE6BF84-94ED-4890-B827-18985C71278B}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.5" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="6" max="6" width="35.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>165</v>
       </c>
@@ -5077,7 +5212,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
@@ -5099,7 +5234,7 @@
         <v>237700</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>149</v>
       </c>
@@ -5121,7 +5256,7 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>144</v>
       </c>
@@ -5142,7 +5277,7 @@
         <v>75800</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>142</v>
       </c>
@@ -5164,7 +5299,7 @@
         <v>379400</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" t="str">
         <f>F10</f>
@@ -5177,6 +5312,9 @@
       <c r="D8" s="7" t="s">
         <v>154</v>
       </c>
+      <c r="E8" s="64" t="s">
+        <v>203</v>
+      </c>
       <c r="F8" s="29" t="s">
         <v>119</v>
       </c>
@@ -5184,7 +5322,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="63" t="s">
         <v>144</v>
       </c>
@@ -5205,7 +5343,7 @@
         <v>24900</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>142</v>
       </c>
@@ -5227,7 +5365,7 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>142</v>
       </c>
@@ -5249,7 +5387,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="63" t="s">
         <v>144</v>
       </c>
@@ -5264,7 +5402,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>142</v>
       </c>
@@ -5280,7 +5418,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="63" t="s">
         <v>144</v>
       </c>
@@ -5295,7 +5433,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>142</v>
       </c>
@@ -5309,7 +5447,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>144</v>
       </c>
@@ -5322,6 +5460,11 @@
       </c>
       <c r="D16" s="13" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="105" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -5333,36 +5476,36 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07797E3D-A485-42C3-B53F-3E8DDE80D453}">
   <dimension ref="A1:AA32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" customWidth="1"/>
-    <col min="6" max="6" width="11.5" customWidth="1"/>
-    <col min="7" max="8" width="8.6640625" customWidth="1"/>
-    <col min="9" max="9" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="8.6640625" customWidth="1"/>
-    <col min="16" max="16" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="23" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="8" width="8.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="8.7109375" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="8.7109375" customWidth="1"/>
+    <col min="23" max="23" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H1" s="1"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="5"/>
-      <c r="O1" s="100" t="s">
+      <c r="O1" s="98" t="s">
         <v>184</v>
       </c>
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
       <c r="S1" s="5"/>
-      <c r="V1" s="100" t="s">
+      <c r="V1" s="98" t="s">
         <v>111</v>
       </c>
       <c r="W1" s="4"/>
@@ -5370,7 +5513,7 @@
       <c r="Y1" s="4"/>
       <c r="Z1" s="5"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
         <v>47</v>
       </c>
@@ -5433,7 +5576,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
         <v>1</v>
       </c>
@@ -5464,7 +5607,7 @@
       <c r="Y3" s="30"/>
       <c r="Z3" s="38"/>
     </row>
-    <row r="4" spans="1:26" ht="30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="39">
         <v>1</v>
       </c>
@@ -5531,7 +5674,7 @@
         <v>63600</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="44">
         <v>8</v>
       </c>
@@ -5598,7 +5741,7 @@
         <v>41250</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="44">
         <v>13</v>
       </c>
@@ -5665,7 +5808,7 @@
         <v>33600</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="44">
         <v>25</v>
       </c>
@@ -5732,7 +5875,7 @@
         <v>51910</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="44">
         <v>29</v>
       </c>
@@ -5799,7 +5942,7 @@
         <v>57960</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="45" t="s">
         <v>46</v>
@@ -5857,7 +6000,7 @@
         <v>248320</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="E10" s="7"/>
       <c r="H10" s="6"/>
@@ -5867,7 +6010,7 @@
       <c r="V10" s="6"/>
       <c r="Z10" s="7"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" t="s">
         <v>133</v>
@@ -5909,7 +6052,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" t="s">
         <v>129</v>
@@ -5951,7 +6094,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="61" t="s">
         <v>137</v>
       </c>
@@ -5969,7 +6112,7 @@
       </c>
       <c r="Z13" s="7"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A14" s="58" t="s">
         <v>132</v>
       </c>
@@ -6020,7 +6163,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>1</v>
       </c>
@@ -6080,7 +6223,7 @@
         <v>50350</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="44">
         <v>8</v>
       </c>
@@ -6141,7 +6284,7 @@
         <v>35750</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="44">
         <v>13</v>
       </c>
@@ -6202,7 +6345,7 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="44">
         <v>25</v>
       </c>
@@ -6263,7 +6406,7 @@
         <v>42920</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="44">
         <v>29</v>
       </c>
@@ -6324,7 +6467,7 @@
         <v>45675</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="45" t="s">
         <v>46</v>
@@ -6394,7 +6537,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="E21" s="7"/>
       <c r="G21" s="33"/>
@@ -6405,7 +6548,7 @@
       <c r="V21" s="6"/>
       <c r="Z21" s="7"/>
     </row>
-    <row r="22" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="74" t="s">
         <v>131</v>
       </c>
@@ -6457,7 +6600,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="30" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>1</v>
       </c>
@@ -6517,7 +6660,7 @@
         <v>13250</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="44">
         <v>8</v>
       </c>
@@ -6577,7 +6720,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="44">
         <v>13</v>
       </c>
@@ -6637,7 +6780,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="44">
         <v>25</v>
       </c>
@@ -6697,7 +6840,7 @@
         <v>8990</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="44">
         <v>29</v>
       </c>
@@ -6757,7 +6900,7 @@
         <v>12285</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
       <c r="B28" s="50" t="s">
         <v>46</v>
@@ -6826,7 +6969,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>62</v>
       </c>
@@ -6864,7 +7007,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>112</v>
       </c>
@@ -6906,7 +7049,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>136</v>
       </c>
@@ -6945,25 +7088,25 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66FE699A-B7D3-4895-957C-B0ACAD52C8FA}">
   <dimension ref="A1:O81"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="81" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="81" customWidth="1"/>
-    <col min="3" max="3" width="4.5" style="81" customWidth="1"/>
-    <col min="4" max="5" width="8.6640625" style="81"/>
-    <col min="6" max="6" width="9.5" style="81" customWidth="1"/>
-    <col min="7" max="7" width="4.1640625" style="81" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="81"/>
+    <col min="1" max="1" width="9.28515625" style="81" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="81" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="81" customWidth="1"/>
+    <col min="4" max="5" width="8.7109375" style="81"/>
+    <col min="6" max="6" width="9.42578125" style="81" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" style="81" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" style="81"/>
     <col min="9" max="9" width="14" style="81" customWidth="1"/>
-    <col min="10" max="10" width="9.83203125" style="81" customWidth="1"/>
-    <col min="11" max="11" width="4.6640625" style="81" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" style="81"/>
-    <col min="13" max="13" width="12.6640625" style="81" customWidth="1"/>
-    <col min="14" max="14" width="9.83203125" style="81" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.6640625" style="81"/>
+    <col min="10" max="10" width="13.140625" style="81" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" style="81" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" style="81"/>
+    <col min="13" max="13" width="12.7109375" style="81" customWidth="1"/>
+    <col min="14" max="14" width="14" style="81" customWidth="1"/>
+    <col min="15" max="16384" width="8.7109375" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="80" t="s">
         <v>96</v>
       </c>
@@ -6974,7 +7117,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="83"/>
       <c r="B2" s="83"/>
       <c r="D2" s="83"/>
@@ -6993,7 +7136,7 @@
       </c>
       <c r="N2" s="83"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="83" t="s">
         <v>47</v>
       </c>
@@ -7028,7 +7171,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="85">
         <v>37104</v>
       </c>
@@ -7052,7 +7195,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="83"/>
       <c r="B5" s="83"/>
       <c r="D5" s="83"/>
@@ -7065,7 +7208,7 @@
       <c r="M5" s="83"/>
       <c r="N5" s="83"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" s="83">
         <v>12</v>
       </c>
@@ -7101,7 +7244,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" s="83"/>
       <c r="B7" s="83"/>
       <c r="D7" s="83"/>
@@ -7126,7 +7269,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="83"/>
       <c r="B8" s="83"/>
       <c r="D8" s="83"/>
@@ -7139,7 +7282,7 @@
       <c r="M8" s="83"/>
       <c r="N8" s="83"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" s="83">
         <v>15</v>
       </c>
@@ -7173,7 +7316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" s="83"/>
       <c r="B10" s="83"/>
       <c r="D10" s="83"/>
@@ -7201,7 +7344,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" s="83"/>
       <c r="B11" s="83"/>
       <c r="D11" s="83"/>
@@ -7214,7 +7357,7 @@
       <c r="M11" s="83"/>
       <c r="N11" s="83"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" s="83">
         <v>21</v>
       </c>
@@ -7250,7 +7393,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" s="83"/>
       <c r="B13" s="83"/>
       <c r="D13" s="83"/>
@@ -7275,7 +7418,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14" s="83"/>
       <c r="B14" s="83"/>
       <c r="D14" s="83"/>
@@ -7288,7 +7431,7 @@
       <c r="M14" s="83"/>
       <c r="N14" s="83"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" s="83">
         <v>22</v>
       </c>
@@ -7322,7 +7465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" s="83"/>
       <c r="B16" s="83"/>
       <c r="D16" s="83"/>
@@ -7352,7 +7495,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A17" s="83"/>
       <c r="B17" s="83"/>
       <c r="D17" s="83"/>
@@ -7365,7 +7508,7 @@
       <c r="M17" s="83"/>
       <c r="N17" s="83"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A18" s="83">
         <v>28</v>
       </c>
@@ -7398,7 +7541,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A19" s="83"/>
       <c r="B19" s="83"/>
       <c r="D19" s="83"/>
@@ -7410,7 +7553,7 @@
       <c r="M19" s="83"/>
       <c r="N19" s="83"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
       <c r="J20" s="86">
         <f>SUM(J9:J18)</f>
         <v>2915</v>
@@ -7426,12 +7569,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A22" s="80" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A23" s="83"/>
       <c r="B23" s="83"/>
       <c r="D23" s="83"/>
@@ -7450,7 +7593,7 @@
       </c>
       <c r="N23" s="83"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A24" s="83" t="s">
         <v>47</v>
       </c>
@@ -7485,7 +7628,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A25" s="85">
         <v>37104</v>
       </c>
@@ -7509,7 +7652,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A26" s="83"/>
       <c r="B26" s="83"/>
       <c r="D26" s="83"/>
@@ -7522,7 +7665,7 @@
       <c r="M26" s="83"/>
       <c r="N26" s="83"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A27" s="83">
         <v>12</v>
       </c>
@@ -7558,7 +7701,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A28" s="83"/>
       <c r="B28" s="83"/>
       <c r="D28" s="83"/>
@@ -7583,7 +7726,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A29" s="83"/>
       <c r="B29" s="83"/>
       <c r="D29" s="83"/>
@@ -7596,7 +7739,7 @@
       <c r="M29" s="83"/>
       <c r="N29" s="83"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A30" s="83">
         <v>15</v>
       </c>
@@ -7631,7 +7774,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A31" s="83"/>
       <c r="B31" s="83"/>
       <c r="D31" s="83"/>
@@ -7662,7 +7805,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A32" s="83"/>
       <c r="B32" s="83"/>
       <c r="D32" s="83"/>
@@ -7675,7 +7818,7 @@
       <c r="M32" s="88"/>
       <c r="N32" s="88"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A33" s="83">
         <v>21</v>
       </c>
@@ -7711,7 +7854,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A34" s="83"/>
       <c r="B34" s="83"/>
       <c r="D34" s="83"/>
@@ -7736,7 +7879,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A35" s="83"/>
       <c r="B35" s="83"/>
       <c r="D35" s="83"/>
@@ -7761,7 +7904,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A36" s="83"/>
       <c r="B36" s="83"/>
       <c r="D36" s="83"/>
@@ -7774,7 +7917,7 @@
       <c r="M36" s="87"/>
       <c r="N36" s="87"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A37" s="83">
         <v>22</v>
       </c>
@@ -7813,7 +7956,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A38" s="83"/>
       <c r="B38" s="83"/>
       <c r="D38" s="83"/>
@@ -7848,7 +7991,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A39" s="83"/>
       <c r="B39" s="83"/>
       <c r="D39" s="83"/>
@@ -7883,7 +8026,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A40" s="83"/>
       <c r="B40" s="83"/>
       <c r="D40" s="83"/>
@@ -7896,7 +8039,7 @@
       <c r="M40" s="87"/>
       <c r="N40" s="87"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A41" s="83">
         <v>28</v>
       </c>
@@ -7932,7 +8075,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A42" s="83"/>
       <c r="B42" s="83"/>
       <c r="D42" s="83"/>
@@ -7964,7 +8107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.4">
       <c r="G43" s="81" t="s">
         <v>105</v>
       </c>
@@ -7991,7 +8134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.4">
       <c r="J45" s="80">
         <f>SUM(J30:J43)</f>
         <v>2990</v>
@@ -8007,12 +8150,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A46" s="81" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A47" s="83"/>
       <c r="B47" s="83"/>
       <c r="D47" s="83"/>
@@ -8031,7 +8174,7 @@
       </c>
       <c r="N47" s="83"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A48" s="83" t="s">
         <v>47</v>
       </c>
@@ -8066,7 +8209,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A49" s="85">
         <v>37104</v>
       </c>
@@ -8090,7 +8233,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A50" s="83"/>
       <c r="B50" s="83"/>
       <c r="D50" s="83"/>
@@ -8103,7 +8246,7 @@
       <c r="M50" s="83"/>
       <c r="N50" s="83"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A51" s="83">
         <v>12</v>
       </c>
@@ -8134,7 +8277,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A52" s="83"/>
       <c r="B52" s="83"/>
       <c r="D52" s="83"/>
@@ -8149,7 +8292,7 @@
       </c>
       <c r="N52" s="83"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A53" s="83">
         <v>15</v>
       </c>
@@ -8179,7 +8322,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A54" s="83"/>
       <c r="B54" s="83"/>
       <c r="D54" s="83"/>
@@ -8192,7 +8335,7 @@
       <c r="M54" s="83"/>
       <c r="N54" s="83"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A55" s="83">
         <v>21</v>
       </c>
@@ -8222,7 +8365,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A56" s="83"/>
       <c r="B56" s="83"/>
       <c r="D56" s="83"/>
@@ -8235,7 +8378,7 @@
       <c r="M56" s="83"/>
       <c r="N56" s="83"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A57" s="83">
         <v>22</v>
       </c>
@@ -8266,7 +8409,7 @@
         <v>1110.3157894736842</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A58" s="83"/>
       <c r="B58" s="83"/>
       <c r="D58" s="83"/>
@@ -8279,7 +8422,7 @@
       <c r="M58" s="83"/>
       <c r="N58" s="83"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A59" s="83">
         <v>28</v>
       </c>
@@ -8310,7 +8453,7 @@
         <v>308.41801169590633</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A60" s="83"/>
       <c r="B60" s="83"/>
       <c r="D60" s="83"/>
@@ -8323,12 +8466,12 @@
       <c r="M60" s="83"/>
       <c r="N60" s="83"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A63" s="81" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A64" s="83"/>
       <c r="B64" s="83"/>
       <c r="D64" s="83"/>
@@ -8347,7 +8490,7 @@
       </c>
       <c r="N64" s="83"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A65" s="83" t="s">
         <v>47</v>
       </c>
@@ -8382,7 +8525,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A66" s="85">
         <v>37104</v>
       </c>
@@ -8406,7 +8549,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A67" s="83"/>
       <c r="B67" s="83"/>
       <c r="D67" s="83"/>
@@ -8419,7 +8562,7 @@
       <c r="M67" s="83"/>
       <c r="N67" s="83"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A68" s="83">
         <v>12</v>
       </c>
@@ -8450,7 +8593,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A69" s="83"/>
       <c r="B69" s="83"/>
       <c r="D69" s="83"/>
@@ -8470,7 +8613,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A70" s="83">
         <v>15</v>
       </c>
@@ -8487,7 +8630,7 @@
       <c r="M70" s="83"/>
       <c r="N70" s="83"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A71" s="83"/>
       <c r="B71" s="83"/>
       <c r="D71" s="83"/>
@@ -8500,7 +8643,7 @@
       <c r="M71" s="83"/>
       <c r="N71" s="83"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A72" s="83"/>
       <c r="B72" s="83"/>
       <c r="D72" s="83"/>
@@ -8513,7 +8656,7 @@
       <c r="M72" s="83"/>
       <c r="N72" s="83"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A73" s="83">
         <v>21</v>
       </c>
@@ -8535,7 +8678,7 @@
       <c r="M73" s="83"/>
       <c r="N73" s="83"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A74" s="83"/>
       <c r="B74" s="83"/>
       <c r="D74" s="83"/>
@@ -8548,7 +8691,7 @@
       <c r="M74" s="83"/>
       <c r="N74" s="83"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A75" s="83"/>
       <c r="B75" s="83"/>
       <c r="D75" s="83"/>
@@ -8561,7 +8704,7 @@
       <c r="M75" s="83"/>
       <c r="N75" s="83"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A76" s="83">
         <v>22</v>
       </c>
@@ -8578,7 +8721,7 @@
       <c r="M76" s="83"/>
       <c r="N76" s="83"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A77" s="83">
         <v>28</v>
       </c>
@@ -8595,7 +8738,7 @@
       <c r="M77" s="83"/>
       <c r="N77" s="83"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.4">
       <c r="I78" s="83"/>
       <c r="J78" s="83"/>
       <c r="L78" s="83">
@@ -8609,7 +8752,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.4">
       <c r="B79" s="83"/>
       <c r="D79" s="83"/>
       <c r="E79" s="83"/>
@@ -8627,7 +8770,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A80" s="83"/>
       <c r="B80" s="83"/>
       <c r="D80" s="83"/>
@@ -8647,7 +8790,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="81" spans="4:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:14" x14ac:dyDescent="0.4">
       <c r="D81" s="81">
         <f>SUM(D66:D79)</f>
         <v>210</v>
@@ -8680,23 +8823,216 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8B168DD-EF48-46C0-9B73-3B7507204614}">
+  <dimension ref="B20:E52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="10.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="102" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="102" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <v>19500</v>
+      </c>
+      <c r="C26" s="100">
+        <v>31</v>
+      </c>
+      <c r="D26" s="100">
+        <v>604500</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>7500</v>
+      </c>
+      <c r="C27" s="100">
+        <v>30</v>
+      </c>
+      <c r="D27" s="100">
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="99">
+        <v>27000</v>
+      </c>
+      <c r="D28" s="101">
+        <v>829500</v>
+      </c>
+      <c r="E28" s="64" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="64" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="102" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="102" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <v>13500</v>
+      </c>
+      <c r="C38" s="100">
+        <v>27</v>
+      </c>
+      <c r="D38" s="100">
+        <v>364500</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39">
+        <v>12750</v>
+      </c>
+      <c r="C39" s="100">
+        <v>28</v>
+      </c>
+      <c r="D39" s="100">
+        <v>357000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40">
+        <v>750</v>
+      </c>
+      <c r="C40" s="100">
+        <v>30</v>
+      </c>
+      <c r="D40" s="100">
+        <v>22500</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="99">
+        <v>27000</v>
+      </c>
+      <c r="D41" s="101">
+        <v>744000</v>
+      </c>
+      <c r="E41" s="64" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B43" s="64" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B45" s="102" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="64" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="64" t="s">
+        <v>202</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6630C2FA-7F47-4646-A4FB-C656FFCA9DC7}">
   <dimension ref="B1:X20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.33203125" customWidth="1"/>
-    <col min="21" max="21" width="6.1640625" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.28515625" customWidth="1"/>
+    <col min="21" max="21" width="6.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="G1" t="s">
         <v>3</v>
       </c>
@@ -8719,7 +9055,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8744,7 +9080,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
       <c r="F3" t="s">
         <v>5</v>
       </c>
@@ -8783,7 +9119,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="2:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
@@ -8815,7 +9151,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
@@ -8837,8 +9173,8 @@
       <c r="W5" s="14"/>
       <c r="X5" s="14"/>
     </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C6" s="97" t="s">
+    <row r="6" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="C6" s="103" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="2"/>
@@ -8875,8 +9211,8 @@
       <c r="W6" s="14"/>
       <c r="X6" s="14"/>
     </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C7" s="97"/>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="C7" s="103"/>
       <c r="D7" s="2"/>
       <c r="E7" s="3" t="s">
         <v>14</v>
@@ -8896,8 +9232,8 @@
       <c r="W7" s="14"/>
       <c r="X7" s="14"/>
     </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C8" s="97"/>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="C8" s="103"/>
       <c r="D8" s="2"/>
       <c r="E8" s="16" t="s">
         <v>24</v>
@@ -8918,8 +9254,8 @@
       <c r="W8" s="14"/>
       <c r="X8" s="14"/>
     </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C9" s="97"/>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="C9" s="103"/>
       <c r="D9" s="2"/>
       <c r="E9" s="3" t="s">
         <v>14</v>
@@ -8935,8 +9271,8 @@
       <c r="W9" s="14"/>
       <c r="X9" s="14"/>
     </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C10" s="97"/>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="C10" s="103"/>
       <c r="D10" s="2"/>
       <c r="E10" s="16" t="s">
         <v>26</v>
@@ -8972,7 +9308,7 @@
       <c r="W10" s="14"/>
       <c r="X10" s="14"/>
     </row>
-    <row r="11" spans="2:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -9002,7 +9338,7 @@
       <c r="W11" s="14"/>
       <c r="X11" s="14"/>
     </row>
-    <row r="12" spans="2:24" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:24" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="3" t="s">
@@ -9019,7 +9355,7 @@
       </c>
       <c r="O12" s="7"/>
     </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C13" s="2" t="s">
         <v>36</v>
       </c>
@@ -9036,7 +9372,7 @@
       <c r="M13" s="6"/>
       <c r="O13" s="7"/>
     </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
         <v>39</v>
       </c>
@@ -9054,7 +9390,7 @@
       </c>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
       <c r="M15" s="6" t="s">
         <v>41</v>
       </c>
@@ -9062,17 +9398,17 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
       <c r="M16" s="6" t="s">
         <v>42</v>
       </c>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="11:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="11:15" x14ac:dyDescent="0.25">
       <c r="M17" s="6"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="11:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K18">
         <v>4</v>
       </c>
@@ -9087,7 +9423,7 @@
       </c>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="11:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="11:15" x14ac:dyDescent="0.25">
       <c r="M19" s="6" t="s">
         <v>44</v>
       </c>
@@ -9095,7 +9431,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="11:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="11:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M20" s="11" t="s">
         <v>45</v>
       </c>
@@ -9116,24 +9452,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{621C8771-121C-4028-A96C-339990C7F79F}">
   <dimension ref="B1:I18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.1640625" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.5" customWidth="1"/>
-    <col min="8" max="8" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G1" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="17" t="s">
         <v>63</v>
       </c>
@@ -9141,13 +9477,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="17"/>
       <c r="C3" s="18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
       <c r="E4" t="s">
@@ -9166,8 +9502,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B5" s="98" t="s">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="104" t="s">
         <v>69</v>
       </c>
       <c r="C5" s="17" t="s">
@@ -9192,8 +9528,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B6" s="98"/>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="104"/>
       <c r="C6" s="18" t="s">
         <v>14</v>
       </c>
@@ -9213,12 +9549,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B7" s="98"/>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="104"/>
       <c r="C7" s="18"/>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="98"/>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="104"/>
       <c r="C8" s="17" t="s">
         <v>82</v>
       </c>
@@ -9235,8 +9571,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B9" s="98"/>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="104"/>
       <c r="C9" s="18" t="s">
         <v>14</v>
       </c>
@@ -9250,8 +9586,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B10" s="98"/>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="104"/>
       <c r="C10" s="18"/>
       <c r="E10" t="s">
         <v>89</v>
@@ -9260,23 +9596,23 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B11" s="98"/>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="104"/>
       <c r="C11" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="17"/>
       <c r="C12" s="18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="17"/>
       <c r="C13" s="18"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="17" t="s">
         <v>91</v>
       </c>
@@ -9284,25 +9620,25 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="17"/>
       <c r="C15" s="19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="17"/>
       <c r="C16" s="19" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="17"/>
       <c r="C17" s="19" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="17"/>
       <c r="C18" s="19" t="s">
         <v>95</v>
@@ -9322,45 +9658,45 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{452F9814-F5FC-433D-A91B-A1506DD05597}">
   <dimension ref="B2:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.83203125" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="25"/>
       <c r="C4" s="26"/>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="27"/>
       <c r="C5" s="28"/>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="29"/>
       <c r="C6" s="28"/>
     </row>
-    <row r="7" spans="2:3" ht="3" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:3" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="29"/>
       <c r="C7" s="28"/>
     </row>
-    <row r="8" spans="2:3" ht="9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="B8" s="29"/>
       <c r="C8" s="28"/>
     </row>
-    <row r="9" spans="2:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="B9" s="29"/>
       <c r="C9" s="28"/>
     </row>
-    <row r="10" spans="2:3" ht="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="B10" s="29"/>
       <c r="C10" s="28"/>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="29"/>
       <c r="C11" s="28"/>
     </row>
@@ -9372,17 +9708,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34499A49-CA92-4EBB-8E34-607384C2C107}">
   <dimension ref="B2:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.83203125" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
         <v>112</v>
       </c>
@@ -9390,7 +9726,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="27" t="s">
         <v>114</v>
       </c>
@@ -9398,7 +9734,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
         <v>116</v>
       </c>
@@ -9406,7 +9742,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="29" t="s">
         <v>62</v>
       </c>
@@ -9414,7 +9750,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="29" t="s">
         <v>119</v>
       </c>
@@ -9422,7 +9758,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="29" t="s">
         <v>121</v>
       </c>
@@ -9430,7 +9766,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="29" t="s">
         <v>123</v>
       </c>
@@ -9438,7 +9774,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="29" t="s">
         <v>125</v>
       </c>
@@ -9454,26 +9790,26 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D8F79D-9820-4F0E-85E0-EB2FC36CCDA0}">
   <dimension ref="A1:O83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="81" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="81" customWidth="1"/>
-    <col min="3" max="3" width="4.5" style="81" customWidth="1"/>
-    <col min="4" max="5" width="8.6640625" style="81"/>
-    <col min="6" max="6" width="9.5" style="81" customWidth="1"/>
-    <col min="7" max="7" width="6.33203125" style="81" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" style="81"/>
-    <col min="11" max="11" width="4.6640625" style="81" customWidth="1"/>
-    <col min="12" max="12" width="16.5" style="81" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="81"/>
+    <col min="1" max="1" width="9.28515625" style="81" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="81" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="81" customWidth="1"/>
+    <col min="4" max="5" width="8.7109375" style="81"/>
+    <col min="6" max="6" width="9.42578125" style="81" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" style="81" customWidth="1"/>
+    <col min="8" max="10" width="8.7109375" style="81"/>
+    <col min="11" max="11" width="4.7109375" style="81" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" style="81" customWidth="1"/>
+    <col min="13" max="16384" width="8.7109375" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="80" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="83"/>
       <c r="B2" s="83"/>
       <c r="D2" s="83"/>
@@ -9492,7 +9828,7 @@
       </c>
       <c r="N2" s="83"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="83" t="s">
         <v>47</v>
       </c>
@@ -9527,7 +9863,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="85">
         <v>37104</v>
       </c>
@@ -9551,7 +9887,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="83"/>
       <c r="B5" s="83"/>
       <c r="D5" s="83"/>
@@ -9564,7 +9900,7 @@
       <c r="M5" s="83"/>
       <c r="N5" s="83"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" s="83">
         <v>12</v>
       </c>
@@ -9600,7 +9936,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" s="83"/>
       <c r="B7" s="83"/>
       <c r="D7" s="83"/>
@@ -9625,7 +9961,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="83"/>
       <c r="B8" s="83"/>
       <c r="D8" s="83"/>
@@ -9638,7 +9974,7 @@
       <c r="M8" s="83"/>
       <c r="N8" s="83"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" s="83">
         <v>15</v>
       </c>
@@ -9672,7 +10008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" s="83"/>
       <c r="B10" s="83"/>
       <c r="D10" s="83"/>
@@ -9700,7 +10036,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" s="83"/>
       <c r="B11" s="83"/>
       <c r="D11" s="83"/>
@@ -9713,7 +10049,7 @@
       <c r="M11" s="83"/>
       <c r="N11" s="83"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" s="83">
         <v>21</v>
       </c>
@@ -9749,7 +10085,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" s="83"/>
       <c r="B13" s="83"/>
       <c r="D13" s="83"/>
@@ -9774,7 +10110,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14" s="83"/>
       <c r="B14" s="83"/>
       <c r="D14" s="83"/>
@@ -9787,7 +10123,7 @@
       <c r="M14" s="83"/>
       <c r="N14" s="83"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" s="83">
         <v>22</v>
       </c>
@@ -9821,7 +10157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" s="83"/>
       <c r="B16" s="83"/>
       <c r="D16" s="83"/>
@@ -9851,7 +10187,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A17" s="83"/>
       <c r="B17" s="83"/>
       <c r="D17" s="83"/>
@@ -9864,7 +10200,7 @@
       <c r="M17" s="83"/>
       <c r="N17" s="83"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A18" s="83">
         <v>28</v>
       </c>
@@ -9900,7 +10236,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A19" s="83"/>
       <c r="B19" s="83"/>
       <c r="D19" s="83"/>
@@ -9912,7 +10248,7 @@
       <c r="M19" s="83"/>
       <c r="N19" s="83"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
       <c r="J20" s="86">
         <f>SUM(J9:J18)</f>
         <v>2915</v>
@@ -9928,7 +10264,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
       <c r="K21" s="81" t="s">
         <v>177</v>
       </c>
@@ -9936,12 +10272,12 @@
         <v>178</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A22" s="80" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A23" s="83"/>
       <c r="B23" s="83"/>
       <c r="D23" s="83"/>
@@ -9960,7 +10296,7 @@
       </c>
       <c r="N23" s="83"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A24" s="83" t="s">
         <v>47</v>
       </c>
@@ -9995,7 +10331,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A25" s="85">
         <v>37104</v>
       </c>
@@ -10019,7 +10355,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A26" s="83"/>
       <c r="B26" s="83"/>
       <c r="D26" s="83"/>
@@ -10032,7 +10368,7 @@
       <c r="M26" s="83"/>
       <c r="N26" s="83"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A27" s="83">
         <v>12</v>
       </c>
@@ -10068,7 +10404,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A28" s="83"/>
       <c r="B28" s="83"/>
       <c r="D28" s="83"/>
@@ -10093,7 +10429,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A29" s="83"/>
       <c r="B29" s="83"/>
       <c r="D29" s="83"/>
@@ -10106,7 +10442,7 @@
       <c r="M29" s="83"/>
       <c r="N29" s="83"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A30" s="83">
         <v>15</v>
       </c>
@@ -10141,7 +10477,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A31" s="83"/>
       <c r="B31" s="83"/>
       <c r="D31" s="83"/>
@@ -10172,7 +10508,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A32" s="83"/>
       <c r="B32" s="83"/>
       <c r="D32" s="83"/>
@@ -10185,7 +10521,7 @@
       <c r="M32" s="88"/>
       <c r="N32" s="88"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A33" s="83">
         <v>21</v>
       </c>
@@ -10221,7 +10557,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A34" s="83"/>
       <c r="B34" s="83"/>
       <c r="D34" s="83"/>
@@ -10246,7 +10582,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A35" s="83"/>
       <c r="B35" s="83"/>
       <c r="D35" s="83"/>
@@ -10271,7 +10607,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A36" s="83"/>
       <c r="B36" s="83"/>
       <c r="D36" s="83"/>
@@ -10284,7 +10620,7 @@
       <c r="M36" s="87"/>
       <c r="N36" s="87"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A37" s="83">
         <v>22</v>
       </c>
@@ -10323,7 +10659,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A38" s="83"/>
       <c r="B38" s="83"/>
       <c r="D38" s="83"/>
@@ -10358,7 +10694,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A39" s="83"/>
       <c r="B39" s="83"/>
       <c r="D39" s="83"/>
@@ -10393,7 +10729,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A40" s="83"/>
       <c r="B40" s="83"/>
       <c r="D40" s="83"/>
@@ -10406,7 +10742,7 @@
       <c r="M40" s="87"/>
       <c r="N40" s="87"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A41" s="83">
         <v>28</v>
       </c>
@@ -10442,7 +10778,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A42" s="83"/>
       <c r="B42" s="83"/>
       <c r="D42" s="83"/>
@@ -10474,7 +10810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.4">
       <c r="G43" s="81" t="s">
         <v>105</v>
       </c>
@@ -10501,7 +10837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.4">
       <c r="J45" s="80">
         <f>SUM(J30:J43)</f>
         <v>2990</v>
@@ -10517,12 +10853,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A46" s="81" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A47" s="83"/>
       <c r="B47" s="83"/>
       <c r="D47" s="83"/>
@@ -10541,7 +10877,7 @@
       </c>
       <c r="N47" s="83"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A48" s="83" t="s">
         <v>47</v>
       </c>
@@ -10576,7 +10912,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A49" s="85">
         <v>37104</v>
       </c>
@@ -10600,7 +10936,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A50" s="83"/>
       <c r="B50" s="83"/>
       <c r="D50" s="83"/>
@@ -10613,7 +10949,7 @@
       <c r="M50" s="83"/>
       <c r="N50" s="83"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A51" s="83">
         <v>12</v>
       </c>
@@ -10644,7 +10980,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A52" s="83"/>
       <c r="B52" s="83"/>
       <c r="D52" s="83"/>
@@ -10657,7 +10993,7 @@
       <c r="M52" s="83"/>
       <c r="N52" s="83"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A53" s="83">
         <v>15</v>
       </c>
@@ -10689,7 +11025,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A54" s="83"/>
       <c r="B54" s="83"/>
       <c r="D54" s="83"/>
@@ -10702,7 +11038,7 @@
       <c r="M54" s="83"/>
       <c r="N54" s="83"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A55" s="83">
         <v>21</v>
       </c>
@@ -10733,7 +11069,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A56" s="83"/>
       <c r="B56" s="83"/>
       <c r="D56" s="83"/>
@@ -10746,7 +11082,7 @@
       <c r="M56" s="83"/>
       <c r="N56" s="83"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A57" s="83">
         <v>22</v>
       </c>
@@ -10778,7 +11114,7 @@
         <v>1110.3157894736844</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A58" s="83"/>
       <c r="B58" s="83"/>
       <c r="D58" s="83"/>
@@ -10791,7 +11127,7 @@
       <c r="M58" s="83"/>
       <c r="N58" s="83"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A59" s="83">
         <v>28</v>
       </c>
@@ -10823,7 +11159,7 @@
         <v>308.42105263157896</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A60" s="83"/>
       <c r="B60" s="83"/>
       <c r="D60" s="83"/>
@@ -10836,7 +11172,7 @@
       <c r="M60" s="83"/>
       <c r="N60" s="83"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.4">
       <c r="H61" s="81">
         <f>SUM(H53:H59)</f>
         <v>245</v>
@@ -10856,7 +11192,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A63" s="81" t="s">
         <v>111</v>
       </c>
@@ -10864,7 +11200,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A64" s="83"/>
       <c r="B64" s="83"/>
       <c r="D64" s="83"/>
@@ -10883,7 +11219,7 @@
       </c>
       <c r="N64" s="83"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A65" s="83" t="s">
         <v>47</v>
       </c>
@@ -10918,7 +11254,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A66" s="85">
         <v>37104</v>
       </c>
@@ -10942,7 +11278,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A67" s="83"/>
       <c r="B67" s="83"/>
       <c r="D67" s="83"/>
@@ -10955,7 +11291,7 @@
       <c r="M67" s="83"/>
       <c r="N67" s="83"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A68" s="83">
         <v>12</v>
       </c>
@@ -10977,7 +11313,7 @@
       <c r="M68" s="83"/>
       <c r="N68" s="83"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A69" s="83"/>
       <c r="B69" s="83"/>
       <c r="D69" s="83"/>
@@ -10990,7 +11326,7 @@
       <c r="M69" s="83"/>
       <c r="N69" s="83"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A70" s="83">
         <v>15</v>
       </c>
@@ -11005,7 +11341,7 @@
       <c r="M70" s="83"/>
       <c r="N70" s="83"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A71" s="83"/>
       <c r="B71" s="83"/>
       <c r="D71" s="83"/>
@@ -11018,7 +11354,7 @@
       <c r="M71" s="83"/>
       <c r="N71" s="83"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A72" s="83"/>
       <c r="B72" s="83"/>
       <c r="D72" s="83"/>
@@ -11031,7 +11367,7 @@
       <c r="M72" s="83"/>
       <c r="N72" s="83"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A73" s="83">
         <v>21</v>
       </c>
@@ -11053,7 +11389,7 @@
       <c r="M73" s="83"/>
       <c r="N73" s="83"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A74" s="83"/>
       <c r="B74" s="83"/>
       <c r="D74" s="83"/>
@@ -11066,7 +11402,7 @@
       <c r="M74" s="83"/>
       <c r="N74" s="83"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A75" s="83"/>
       <c r="B75" s="83"/>
       <c r="D75" s="83"/>
@@ -11079,7 +11415,7 @@
       <c r="M75" s="83"/>
       <c r="N75" s="83"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A76" s="83"/>
       <c r="B76" s="83"/>
       <c r="D76" s="83"/>
@@ -11092,7 +11428,7 @@
       <c r="M76" s="83"/>
       <c r="N76" s="83"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A77" s="83">
         <v>22</v>
       </c>
@@ -11107,7 +11443,7 @@
       <c r="M77" s="83"/>
       <c r="N77" s="83"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A78" s="83"/>
       <c r="B78" s="83"/>
       <c r="D78" s="83"/>
@@ -11120,7 +11456,7 @@
       <c r="M78" s="83"/>
       <c r="N78" s="83"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A79" s="83">
         <v>28</v>
       </c>
@@ -11147,7 +11483,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A80" s="83"/>
       <c r="B80" s="83"/>
       <c r="D80" s="83"/>
@@ -11172,7 +11508,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:14" x14ac:dyDescent="0.4">
       <c r="H81" s="81">
         <v>112</v>
       </c>
@@ -11192,8 +11528,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="83" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B83" s="99" t="s">
+    <row r="83" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B83" s="97" t="s">
         <v>183</v>
       </c>
     </row>
@@ -11207,22 +11543,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1844EA51-03FA-4C78-8619-78C342259328}">
   <dimension ref="A1:AA32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.5" customWidth="1"/>
-    <col min="7" max="8" width="8.6640625" customWidth="1"/>
-    <col min="9" max="9" width="17.1640625" customWidth="1"/>
-    <col min="10" max="15" width="8.6640625" customWidth="1"/>
-    <col min="16" max="16" width="17.1640625" customWidth="1"/>
-    <col min="17" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="23" width="17.1640625" customWidth="1"/>
-    <col min="24" max="26" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="8" width="8.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" customWidth="1"/>
+    <col min="10" max="15" width="8.7109375" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" customWidth="1"/>
+    <col min="17" max="22" width="8.7109375" customWidth="1"/>
+    <col min="23" max="23" width="17.140625" customWidth="1"/>
+    <col min="24" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H1" s="1"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
@@ -11239,7 +11575,7 @@
       <c r="Y1" s="4"/>
       <c r="Z1" s="5"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
         <v>47</v>
       </c>
@@ -11302,7 +11638,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
         <v>1</v>
       </c>
@@ -11333,7 +11669,7 @@
       <c r="Y3" s="30"/>
       <c r="Z3" s="38"/>
     </row>
-    <row r="4" spans="1:26" ht="30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="39">
         <v>1</v>
       </c>
@@ -11400,7 +11736,7 @@
         <v>63600</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="44">
         <v>8</v>
       </c>
@@ -11467,7 +11803,7 @@
         <v>41250</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="44">
         <v>13</v>
       </c>
@@ -11534,7 +11870,7 @@
         <v>33600</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="44">
         <v>25</v>
       </c>
@@ -11601,7 +11937,7 @@
         <v>51910</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="44">
         <v>29</v>
       </c>
@@ -11668,7 +12004,7 @@
         <v>57960</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="45" t="s">
         <v>46</v>
@@ -11726,7 +12062,7 @@
         <v>248320</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="E10" s="7"/>
       <c r="H10" s="6"/>
@@ -11736,7 +12072,7 @@
       <c r="V10" s="6"/>
       <c r="Z10" s="7"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" t="s">
         <v>133</v>
@@ -11778,7 +12114,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" t="s">
         <v>129</v>
@@ -11820,7 +12156,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="61" t="s">
         <v>137</v>
       </c>
@@ -11838,7 +12174,7 @@
       </c>
       <c r="Z13" s="7"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A14" s="58" t="s">
         <v>132</v>
       </c>
@@ -11889,7 +12225,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>1</v>
       </c>
@@ -11949,7 +12285,7 @@
         <v>50350</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="44">
         <v>8</v>
       </c>
@@ -12010,7 +12346,7 @@
         <v>35750</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="44">
         <v>13</v>
       </c>
@@ -12071,7 +12407,7 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="44">
         <v>25</v>
       </c>
@@ -12132,7 +12468,7 @@
         <v>42920</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="44">
         <v>29</v>
       </c>
@@ -12193,7 +12529,7 @@
         <v>45675</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="45" t="s">
         <v>46</v>
@@ -12253,7 +12589,7 @@
         <v>202695</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="E21" s="7"/>
       <c r="G21" s="33"/>
@@ -12264,7 +12600,7 @@
       <c r="V21" s="6"/>
       <c r="Z21" s="7"/>
     </row>
-    <row r="22" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="74" t="s">
         <v>131</v>
       </c>
@@ -12316,7 +12652,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="30" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>1</v>
       </c>
@@ -12376,7 +12712,7 @@
         <v>13250</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="44">
         <v>8</v>
       </c>
@@ -12436,7 +12772,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="44">
         <v>13</v>
       </c>
@@ -12496,7 +12832,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="44">
         <v>25</v>
       </c>
@@ -12556,7 +12892,7 @@
         <v>8990</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="44">
         <v>29</v>
       </c>
@@ -12616,7 +12952,7 @@
         <v>12285</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
       <c r="B28" s="50" t="s">
         <v>46</v>
@@ -12675,7 +13011,7 @@
         <v>45625</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>62</v>
       </c>
@@ -12713,7 +13049,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>112</v>
       </c>
@@ -12755,7 +13091,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>136</v>
       </c>
@@ -12794,9 +13130,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16B2D650-A5EC-4232-8ED2-89227865BE4D}">
   <dimension ref="B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>141</v>
       </c>
@@ -12810,7 +13146,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E3D6BC-EBCC-4192-91D8-66369F108705}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
